--- a/tools/importer/reports/import-html-sitemap.report.xlsx
+++ b/tools/importer/reports/import-html-sitemap.report.xlsx
@@ -82,7 +82,7 @@
     <t>html-sitemap</t>
   </si>
   <si>
-    <t>2026-10-08T04:13:51.746Z</t>
+    <t>2026-10-13T15:22:08.650Z</t>
   </si>
   <si>
     <t>HTML Sitemap</t>
@@ -103,7 +103,7 @@
     <t>content-landing-page</t>
   </si>
   <si>
-    <t>2026-10-06T07:03:54.141Z</t>
+    <t>2026-10-13T15:19:52.095Z</t>
   </si>
   <si>
     <t>Home - Pet Care Network | Destination Pet</t>
@@ -136,7 +136,7 @@
     <t>live-webinar</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:37.067Z</t>
+    <t>2026-10-13T15:20:32.988Z</t>
   </si>
   <si>
     <t>A Series of Webinars | Destination Pet</t>
@@ -163,7 +163,7 @@
     <t>our-locations</t>
   </si>
   <si>
-    <t>2026-10-06T10:14:10.501Z</t>
+    <t>2026-10-13T15:20:59.607Z</t>
   </si>
   <si>
     <t>Our Locations | Destination Pet</t>
@@ -181,7 +181,7 @@
     <t>legal-text-page</t>
   </si>
   <si>
-    <t>2026-10-06T10:13:55.707Z</t>
+    <t>2026-10-13T15:21:36.565Z</t>
   </si>
   <si>
     <t>Privacy Policy | Destination Pet</t>
@@ -199,7 +199,7 @@
     <t>sell-your-business</t>
   </si>
   <si>
-    <t>2026-10-06T07:05:13.807Z</t>
+    <t>2026-10-13T15:21:05.928Z</t>
   </si>
   <si>
     <t>Sell Your Veterinary | Destination Pet</t>
@@ -214,7 +214,7 @@
     <t>terms-and-conditions</t>
   </si>
   <si>
-    <t>2026-10-06T10:14:00.562Z</t>
+    <t>2026-10-13T15:21:41.799Z</t>
   </si>
   <si>
     <t>Terms and Conditions | Destination Pet</t>
@@ -232,7 +232,7 @@
     <t>about-us/about</t>
   </si>
   <si>
-    <t>2026-10-06T07:03:59.368Z</t>
+    <t>2026-10-13T15:19:57.662Z</t>
   </si>
   <si>
     <t>About Us | Destination Pet, LLC</t>
@@ -247,7 +247,7 @@
     <t>about-us/ccpa-request</t>
   </si>
   <si>
-    <t>2026-10-06T10:13:44.507Z</t>
+    <t>2026-10-13T15:21:24.482Z</t>
   </si>
   <si>
     <t>CCPA Request - Destination Pet</t>
@@ -268,7 +268,7 @@
     <t>hero-feature-showcase</t>
   </si>
   <si>
-    <t>2026-10-06T10:43:45.520Z</t>
+    <t>2026-10-13T15:21:50.145Z</t>
   </si>
   <si>
     <t>Destination Pet Foundation - Destination Pet</t>
@@ -286,7 +286,7 @@
     <t>about-us/get-in-touch</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:06.632Z</t>
+    <t>2026-10-13T15:20:04.813Z</t>
   </si>
   <si>
     <t>Contact Us | Destination Pet, LLC</t>
@@ -319,7 +319,7 @@
     <t>about-us/tradeshows-events</t>
   </si>
   <si>
-    <t>2026-10-06T10:13:50.431Z</t>
+    <t>2026-10-13T15:21:30.642Z</t>
   </si>
   <si>
     <t>Tradeshows - Events - Destination Pet</t>
@@ -334,7 +334,7 @@
     <t>join-our-pack/find-a-veterinary-externship</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:26.193Z</t>
+    <t>2026-10-13T15:20:23.797Z</t>
   </si>
   <si>
     <t>Find a Veterinary Externship - Destination Pet</t>
@@ -352,7 +352,7 @@
     <t>join-our-pack/life-at-dp</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:32.565Z</t>
+    <t>2026-10-13T15:20:27.908Z</t>
   </si>
   <si>
     <t>life at Destination Pet | Destination Pet</t>
@@ -370,7 +370,7 @@
     <t>live-webinar/webinar-redirect</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:42.325Z</t>
+    <t>2026-10-13T15:20:36.986Z</t>
   </si>
   <si>
     <t>Webinar Redirect - Destination Pet</t>
@@ -385,7 +385,7 @@
     <t>live-webinar/webinar-registration</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:47.899Z</t>
+    <t>2026-10-13T15:20:42.646Z</t>
   </si>
   <si>
     <t>Webinar Registration - Destination Pet</t>
@@ -400,7 +400,7 @@
     <t>live-webinar/webinar-viewing-previous</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:53.143Z</t>
+    <t>2026-10-13T15:20:48.822Z</t>
   </si>
   <si>
     <t>Webinar Viewing Previous - Destination Pet</t>
@@ -415,7 +415,7 @@
     <t>live-webinar/webinars-for-pet</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:59.003Z</t>
+    <t>2026-10-13T15:20:53.204Z</t>
   </si>
   <si>
     <t>Webinars for Pet - Destination Pet</t>
@@ -436,7 +436,7 @@
     <t>location-finder</t>
   </si>
   <si>
-    <t>2026-10-07T15:24:53.311Z</t>
+    <t>2026-10-13T15:21:59.643Z</t>
   </si>
   <si>
     <t>Spot our Location | Destination Pet</t>
@@ -454,7 +454,7 @@
     <t>sell-your-business/sell-your-pet-resort</t>
   </si>
   <si>
-    <t>2026-10-06T07:05:18.864Z</t>
+    <t>2026-10-13T15:21:11.714Z</t>
   </si>
   <si>
     <t>Sell Your Pet Resort - Destination Pet</t>
@@ -472,7 +472,7 @@
     <t>sell-your-business/sell-your-veterinary-practice</t>
   </si>
   <si>
-    <t>2026-10-06T07:05:23.774Z</t>
+    <t>2026-10-13T15:21:16.461Z</t>
   </si>
   <si>
     <t>Sell your veterinary practice | Destination Pet</t>
@@ -487,7 +487,7 @@
     <t>about-us/meet-the-team/business-development-leaders</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:12.956Z</t>
+    <t>2026-10-13T15:20:11.055Z</t>
   </si>
   <si>
     <t>Business Development Leaders | Destination Pet</t>
@@ -502,7 +502,7 @@
     <t>about-us/meet-the-team/leadership</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:18.758Z</t>
+    <t>2026-10-13T15:20:16.502Z</t>
   </si>
   <si>
     <t>Leadership - Meet the team | Destination Pet</t>
